--- a/astro-site/public/dl/kit-tareas-pasteleria/BONUS-01-briefing-servicio.xlsx
+++ b/astro-site/public/dl/kit-tareas-pasteleria/BONUS-01-briefing-servicio.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Briefing Diario" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Briefing Diario" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Briefing Diario'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -89,6 +91,12 @@
       <name val="Calibri"/>
       <color rgb="00999999"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="7">
@@ -129,7 +137,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -151,59 +159,109 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="29">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="6" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -565,13 +623,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B7"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -579,6 +638,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -607,8 +667,24 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «Hecha» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -617,18 +693,18 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -645,10 +721,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -688,18 +765,16 @@
           <t xml:space="preserve">  Producción del Día</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="27" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="28" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -725,10 +800,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="28" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -754,10 +827,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="28" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -783,10 +854,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="28" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -811,24 +880,23 @@
       <c r="F9" s="14" t="n"/>
       <c r="G9" s="15" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Pedidos y Encargos Especiales</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n"/>
-      <c r="C11" s="17" t="n"/>
-      <c r="D11" s="17" t="n"/>
-      <c r="E11" s="17" t="n"/>
-      <c r="F11" s="17" t="n"/>
-      <c r="G11" s="17" t="n"/>
+      <c r="B11" s="26" t="n"/>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="26" t="n"/>
+      <c r="F11" s="26" t="n"/>
+      <c r="G11" s="27" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="28" t="n">
+        <v>5</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
@@ -854,10 +922,8 @@
       <c r="G12" s="15" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="28" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -883,10 +949,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="28" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -911,24 +975,23 @@
       <c r="F14" s="14" t="n"/>
       <c r="G14" s="15" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  Alertas del Día</t>
         </is>
       </c>
-      <c r="B16" s="20" t="n"/>
-      <c r="C16" s="20" t="n"/>
-      <c r="D16" s="20" t="n"/>
-      <c r="E16" s="20" t="n"/>
-      <c r="F16" s="20" t="n"/>
-      <c r="G16" s="20" t="n"/>
+      <c r="B16" s="26" t="n"/>
+      <c r="C16" s="26" t="n"/>
+      <c r="D16" s="26" t="n"/>
+      <c r="E16" s="26" t="n"/>
+      <c r="F16" s="26" t="n"/>
+      <c r="G16" s="27" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="28" t="n">
+        <v>8</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -954,10 +1017,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="28" t="n">
+        <v>9</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -983,10 +1044,8 @@
       <c r="G18" s="15" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="28" t="n">
+        <v>10</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -1012,10 +1071,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="28" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -1040,24 +1097,23 @@
       <c r="F20" s="14" t="n"/>
       <c r="G20" s="15" t="n"/>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  Equipo del Turno</t>
         </is>
       </c>
-      <c r="B22" s="20" t="n"/>
-      <c r="C22" s="20" t="n"/>
-      <c r="D22" s="20" t="n"/>
-      <c r="E22" s="20" t="n"/>
-      <c r="F22" s="20" t="n"/>
-      <c r="G22" s="20" t="n"/>
+      <c r="B22" s="26" t="n"/>
+      <c r="C22" s="26" t="n"/>
+      <c r="D22" s="26" t="n"/>
+      <c r="E22" s="26" t="n"/>
+      <c r="F22" s="26" t="n"/>
+      <c r="G22" s="27" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="28" t="n">
+        <v>12</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -1083,10 +1139,8 @@
       <c r="G23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="28" t="n">
+        <v>13</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
@@ -1112,10 +1166,8 @@
       <c r="G24" s="15" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="28" t="n">
+        <v>14</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
@@ -1140,6 +1192,8 @@
       <c r="F25" s="14" t="n"/>
       <c r="G25" s="15" t="n"/>
     </row>
+    <row r="26"/>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="22" t="inlineStr">
         <is>
@@ -1148,7 +1202,7 @@
       </c>
       <c r="D28" s="22">
         <f>COUNTIF(F5:F26,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
@@ -1159,6 +1213,7 @@
         <v>14</v>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="22" t="inlineStr">
         <is>
@@ -1166,13 +1221,17 @@
         </is>
       </c>
       <c r="B30" s="15" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="27" t="n"/>
       <c r="E30" s="22" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F30" s="15" t="n"/>
-    </row>
+      <c r="G30" s="27" t="n"/>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="24" t="inlineStr">
         <is>
@@ -1193,10 +1252,19 @@
     <mergeCell ref="A28:C28"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F12 F13 F14 F17 F18 F19 F20 F23 F24 F25" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F17 F18 F19 F20 F23 F24 F25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-pasteleria/BONUS-01-briefing-servicio.xlsx
+++ b/astro-site/public/dl/kit-tareas-pasteleria/BONUS-01-briefing-servicio.xlsx
@@ -261,6 +261,16 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -623,7 +633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -667,18 +677,26 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="B9" s="25" t="inlineStr">
-        <is>
-          <t>Marca con ✓ en la columna «Hecha» (desplegable): es la que cuenta el total de tareas completadas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="24" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
+    <row r="8">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>▸ Se usa dos veces al día: al arrancar el obrador y en la apertura de la tienda → 08 Apertura y Cierre del Negocio</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -695,7 +713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -750,7 +768,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -793,7 +811,7 @@
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>Inicio de turno</t>
         </is>
       </c>
       <c r="F6" s="14" t="n"/>
@@ -820,7 +838,7 @@
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>Inicio de turno</t>
         </is>
       </c>
       <c r="F7" s="14" t="n"/>
@@ -847,7 +865,7 @@
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>Inicio de turno</t>
         </is>
       </c>
       <c r="F8" s="14" t="n"/>
@@ -874,7 +892,7 @@
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>Inicio de turno</t>
         </is>
       </c>
       <c r="F9" s="14" t="n"/>
@@ -900,7 +918,7 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Tartas de encargo: nombre cliente, hora recogida, detalles</t>
+          <t>Tartas de encargo: nombre cliente, hora recogida, detalles → 11 Control de Encargos · Ficha de Encargo</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
@@ -915,7 +933,7 @@
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>Inicio de turno</t>
         </is>
       </c>
       <c r="F12" s="14" t="n"/>
@@ -942,7 +960,7 @@
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>Inicio de turno</t>
         </is>
       </c>
       <c r="F13" s="14" t="n"/>
@@ -969,7 +987,7 @@
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>Inicio de turno</t>
         </is>
       </c>
       <c r="F14" s="14" t="n"/>
@@ -995,7 +1013,7 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Alérgenos: productos con alérgenos especiales hoy</t>
+          <t>Alérgenos: productos con alérgenos especiales hoy → 12 Control de Alérgenos de Vitrina</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -1010,7 +1028,7 @@
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>Inicio de turno</t>
         </is>
       </c>
       <c r="F17" s="14" t="n"/>
@@ -1037,7 +1055,7 @@
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>Inicio de turno</t>
         </is>
       </c>
       <c r="F18" s="14" t="n"/>
@@ -1064,7 +1082,7 @@
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>Inicio de turno</t>
         </is>
       </c>
       <c r="F19" s="14" t="n"/>
@@ -1091,7 +1109,7 @@
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>Inicio de turno</t>
         </is>
       </c>
       <c r="F20" s="14" t="n"/>
@@ -1132,7 +1150,7 @@
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>Inicio de turno</t>
         </is>
       </c>
       <c r="F23" s="14" t="n"/>
@@ -1159,7 +1177,7 @@
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>Inicio de turno</t>
         </is>
       </c>
       <c r="F24" s="14" t="n"/>
@@ -1186,54 +1204,90 @@
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>Inicio de turno</t>
         </is>
       </c>
       <c r="F25" s="14" t="n"/>
       <c r="G25" s="15" t="n"/>
     </row>
-    <row r="26"/>
-    <row r="27"/>
+    <row r="26">
+      <c r="A26" s="28" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="21" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="14" t="n"/>
+      <c r="G26" s="15" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="28" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="21" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="14" t="n"/>
+      <c r="G27" s="15" t="n"/>
+    </row>
     <row r="28">
-      <c r="A28" s="22" t="inlineStr">
+      <c r="A28" s="28" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="21" t="n"/>
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="15" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="28" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="21" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="15" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D28" s="22">
-        <f>COUNTIF(F5:F26,"✓")</f>
+      <c r="D31" s="22">
+        <f>COUNTIF(F5:F29,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E28" s="23" t="inlineStr">
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F28" s="22" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="22" t="inlineStr">
+      <c r="F31" s="22">
+        <f>COUNTIF(B5:B29,"?*")</f>
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B30" s="15" t="n"/>
-      <c r="C30" s="26" t="n"/>
-      <c r="D30" s="27" t="n"/>
-      <c r="E30" s="22" t="inlineStr">
+      <c r="B33" s="15" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="27" t="n"/>
+      <c r="E33" s="22" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F30" s="15" t="n"/>
-      <c r="G30" s="27" t="n"/>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="24" t="inlineStr">
+      <c r="F33" s="15" t="n"/>
+      <c r="G33" s="27" t="n"/>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Pastelería / Obrador · AI Chef Pro · aichef.pro</t>
         </is>
@@ -1242,18 +1296,23 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="F33:G33"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A31:C31"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G29">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F17 F18 F19 F20 F23 F24 F25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F17 F18 F19 F20 F23 F24 F25 F26 F27 F28 F29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
